--- a/sample_data.xlsx
+++ b/sample_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Miniproject\ClashFree-Constriant-Based-Timetable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81A17CA-C406-4803-A9DE-7B00C8EA9691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC6AA0E-82C3-4D9F-9CF0-D270ADB13DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
   <si>
     <t>Name</t>
   </si>
@@ -179,6 +179,12 @@
   </si>
   <si>
     <t>Sneha joshi</t>
+  </si>
+  <si>
+    <t>Sumit Mane</t>
+  </si>
+  <si>
+    <t>M3,OS</t>
   </si>
 </sst>
 </file>
@@ -225,11 +231,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -532,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -658,6 +665,23 @@
       </c>
       <c r="E7" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
